--- a/data/kz/15_failure_cases.xlsx
+++ b/data/kz/15_failure_cases.xlsx
@@ -615,6 +615,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1055,7 +1056,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1472,6 +1473,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1831,6 +1833,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2056,7 +2059,7 @@
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
@@ -2182,6 +2185,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
@@ -2189,6 +2193,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
@@ -2249,6 +2254,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
         <is>
@@ -2256,6 +2262,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
         <is>
